--- a/data/theaters-data.xlsx
+++ b/data/theaters-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\2026_KDMHS\공업일반\webprojec\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF95CC77-C443-4505-A8C2-D30D4B7617AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DDC150-356A-49B4-8E7C-59037A89B7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="252">
   <si>
     <t>name</t>
   </si>
@@ -847,6 +847,10 @@
   </si>
   <si>
     <t>../img/theater-thegood.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울특별시 종로구 동숭길 122</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2308,6 +2312,12 @@
       <c r="D46" t="s">
         <v>207</v>
       </c>
+      <c r="G46">
+        <v>37.583373047747799</v>
+      </c>
+      <c r="H46">
+        <v>127.002736308322</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
@@ -2319,6 +2329,12 @@
       <c r="C47" t="s">
         <v>194</v>
       </c>
+      <c r="G47">
+        <v>37.582936689454101</v>
+      </c>
+      <c r="H47">
+        <v>127.00303053803</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
@@ -2330,6 +2346,12 @@
       <c r="C48" t="s">
         <v>195</v>
       </c>
+      <c r="G48">
+        <v>37.582447769293999</v>
+      </c>
+      <c r="H48">
+        <v>127.004345954219</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
@@ -2344,6 +2366,12 @@
       <c r="D49" t="s">
         <v>234</v>
       </c>
+      <c r="G49">
+        <v>37.582260950700203</v>
+      </c>
+      <c r="H49">
+        <v>127.002771590367</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
@@ -2355,6 +2383,12 @@
       <c r="C50" t="s">
         <v>204</v>
       </c>
+      <c r="G50">
+        <v>37.581858090321901</v>
+      </c>
+      <c r="H50">
+        <v>127.003722340943</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
@@ -2366,6 +2400,12 @@
       <c r="C51" t="s">
         <v>235</v>
       </c>
+      <c r="G51">
+        <v>37.581600411337803</v>
+      </c>
+      <c r="H51">
+        <v>127.003553867265</v>
+      </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
@@ -2380,6 +2420,12 @@
       <c r="D52" t="s">
         <v>237</v>
       </c>
+      <c r="G52">
+        <v>37.580754448054698</v>
+      </c>
+      <c r="H52">
+        <v>127.004173774075</v>
+      </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
@@ -2394,6 +2440,12 @@
       <c r="E53" t="s">
         <v>239</v>
       </c>
+      <c r="G53">
+        <v>37.581185519128397</v>
+      </c>
+      <c r="H53">
+        <v>127.002999899724</v>
+      </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
@@ -2431,6 +2483,12 @@
       <c r="E55" t="s">
         <v>226</v>
       </c>
+      <c r="G55">
+        <v>37.581002048349703</v>
+      </c>
+      <c r="H55">
+        <v>127.00396457206701</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
@@ -2448,6 +2506,12 @@
       <c r="E56" t="s">
         <v>227</v>
       </c>
+      <c r="G56">
+        <v>37.576644121319703</v>
+      </c>
+      <c r="H56">
+        <v>127.00393230387</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
@@ -2462,6 +2526,12 @@
       <c r="E57" t="s">
         <v>243</v>
       </c>
+      <c r="G57">
+        <v>37.579919969214203</v>
+      </c>
+      <c r="H57">
+        <v>127.003508390024</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
@@ -2476,6 +2546,12 @@
       <c r="D58" t="s">
         <v>245</v>
       </c>
+      <c r="G58">
+        <v>37.554113462511999</v>
+      </c>
+      <c r="H58">
+        <v>126.92859896038399</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
@@ -2485,10 +2561,16 @@
         <v>196</v>
       </c>
       <c r="C59" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D59" t="s">
         <v>247</v>
+      </c>
+      <c r="G59">
+        <v>37.583699000344602</v>
+      </c>
+      <c r="H59">
+        <v>127.00371665858</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
@@ -2504,6 +2586,12 @@
       <c r="E60" t="s">
         <v>250</v>
       </c>
+      <c r="G60">
+        <v>37.583981592301299</v>
+      </c>
+      <c r="H60">
+        <v>127.002064503637</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
@@ -2515,6 +2603,12 @@
       <c r="C61" t="s">
         <v>248</v>
       </c>
+      <c r="G61">
+        <v>37.583699000344602</v>
+      </c>
+      <c r="H61">
+        <v>127.00371665858</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
@@ -2532,6 +2626,12 @@
       <c r="E62" t="s">
         <v>213</v>
       </c>
+      <c r="G62">
+        <v>37.581375434022299</v>
+      </c>
+      <c r="H62">
+        <v>127.00352713839899</v>
+      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
@@ -2549,6 +2649,12 @@
       <c r="E63" t="s">
         <v>214</v>
       </c>
+      <c r="G63">
+        <v>37.581375434022299</v>
+      </c>
+      <c r="H63">
+        <v>127.00352713839899</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
@@ -2563,8 +2669,14 @@
       <c r="D64" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G64">
+        <v>37.583373047747799</v>
+      </c>
+      <c r="H64">
+        <v>127.002736308322</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>209</v>
       </c>
@@ -2574,8 +2686,14 @@
       <c r="C65" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G65">
+        <v>37.582982829489197</v>
+      </c>
+      <c r="H65">
+        <v>127.00264934489699</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>210</v>
       </c>
@@ -2585,8 +2703,14 @@
       <c r="C66" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G66">
+        <v>37.582982829489197</v>
+      </c>
+      <c r="H66">
+        <v>127.00264934489699</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>219</v>
       </c>
@@ -2602,8 +2726,14 @@
       <c r="E67" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G67">
+        <v>37.582903403238099</v>
+      </c>
+      <c r="H67">
+        <v>127.00430386476</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>221</v>
       </c>
@@ -2619,8 +2749,14 @@
       <c r="E68" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G68">
+        <v>37.582903403238099</v>
+      </c>
+      <c r="H68">
+        <v>127.00430386476</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>229</v>
       </c>
@@ -2635,6 +2771,12 @@
       </c>
       <c r="E69" t="s">
         <v>230</v>
+      </c>
+      <c r="G69">
+        <v>35.1482823676143</v>
+      </c>
+      <c r="H69">
+        <v>129.06547254420701</v>
       </c>
     </row>
   </sheetData>

--- a/data/theaters-data.xlsx
+++ b/data/theaters-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\2026_KDMHS\공업일반\webprojec\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DDC150-356A-49B4-8E7C-59037A89B7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DC04C1-F347-4449-B2BB-50EBD8A11C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="2544" windowWidth="17184" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="256">
   <si>
     <t>name</t>
   </si>
@@ -851,6 +851,21 @@
   </si>
   <si>
     <t>서울특별시 종로구 동숭길 122</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디큐브 링크아트센터</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.d3art.co.kr/</t>
+  </si>
+  <si>
+    <t>서울특별시 구로구 경인로 662</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>../img/theater-cube.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1244,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34.5" customWidth="1"/>
@@ -2779,6 +2794,29 @@
         <v>129.06547254420701</v>
       </c>
     </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>252</v>
+      </c>
+      <c r="B70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C70" t="s">
+        <v>254</v>
+      </c>
+      <c r="D70" t="s">
+        <v>253</v>
+      </c>
+      <c r="E70" t="s">
+        <v>255</v>
+      </c>
+      <c r="G70">
+        <v>37.508123067712901</v>
+      </c>
+      <c r="H70">
+        <v>126.888212953215</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
